--- a/diseases/d236/2000-2004.xlsx
+++ b/diseases/d236/2000-2004.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>6</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -1161,9 +1158,6 @@
       <c r="O4" t="n">
         <v>3</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -1557,9 +1551,6 @@
       <c r="O6" t="n">
         <v>6</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="O8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1336044910704325</v>
       </c>
@@ -2349,9 +2337,6 @@
       <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -2745,9 +2730,6 @@
       <c r="O12" t="n">
         <v>3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -3141,9 +3123,6 @@
       <c r="O14" t="n">
         <v>4</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -3537,9 +3516,6 @@
       <c r="O16" t="n">
         <v>4</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -3933,9 +3909,6 @@
       <c r="O18" t="n">
         <v>7</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.1558719062488379</v>
       </c>
@@ -4329,9 +4302,6 @@
       <c r="O20" t="n">
         <v>3</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.06680224553521626</v>
       </c>
@@ -4725,9 +4695,6 @@
       <c r="O22" t="n">
         <v>4</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.08906966071362167</v>
       </c>
@@ -5121,9 +5088,6 @@
       <c r="O24" t="n">
         <v>14</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.3117438124976759</v>
       </c>
@@ -5517,9 +5481,6 @@
       <c r="O26" t="n">
         <v>9</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0.1993948587586518</v>
       </c>
@@ -5913,9 +5874,6 @@
       <c r="O28" t="n">
         <v>7</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="R28" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -6309,9 +6267,6 @@
       <c r="O30" t="n">
         <v>7</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.1550848901456181</v>
       </c>
@@ -6705,9 +6660,6 @@
       <c r="O32" t="n">
         <v>3</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.0664649529195506</v>
       </c>
@@ -7101,9 +7053,6 @@
       <c r="O34" t="n">
         <v>12</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.2658598116782024</v>
       </c>
@@ -7497,9 +7446,6 @@
       <c r="O36" t="n">
         <v>9</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.1993948587586518</v>
       </c>
@@ -7893,9 +7839,6 @@
       <c r="O38" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -8289,9 +8232,6 @@
       <c r="O40" t="n">
         <v>14</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.3101697802912362</v>
       </c>
@@ -8685,9 +8625,6 @@
       <c r="O42" t="n">
         <v>17</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0.3766347332107867</v>
       </c>
@@ -9081,9 +9018,6 @@
       <c r="O44" t="n">
         <v>10</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -9477,9 +9411,6 @@
       <c r="O46" t="n">
         <v>10</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -9873,9 +9804,6 @@
       <c r="O48" t="n">
         <v>10</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.2215498430651687</v>
       </c>
@@ -10269,9 +10197,6 @@
       <c r="O50" t="n">
         <v>11</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2423967841439008</v>
       </c>
@@ -10665,9 +10590,6 @@
       <c r="O52" t="n">
         <v>8</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -11061,9 +10983,6 @@
       <c r="O54" t="n">
         <v>6</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
       <c r="R54" t="n">
         <v>0.132216427714855</v>
       </c>
@@ -11457,9 +11376,6 @@
       <c r="O56" t="n">
         <v>22</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.4847935682878017</v>
       </c>
@@ -11853,9 +11769,6 @@
       <c r="O58" t="n">
         <v>14</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.3085049980013284</v>
       </c>
@@ -12249,9 +12162,6 @@
       <c r="O60" t="n">
         <v>8</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.1762885702864733</v>
       </c>
@@ -12645,9 +12555,6 @@
       <c r="O62" t="n">
         <v>11</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.2423967841439008</v>
       </c>
@@ -13041,9 +12948,6 @@
       <c r="O64" t="n">
         <v>9</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.1983246415722825</v>
       </c>
@@ -13437,9 +13341,6 @@
       <c r="O66" t="n">
         <v>14</v>
       </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
       <c r="R66" t="n">
         <v>0.3085049980013284</v>
       </c>
@@ -13833,9 +13734,6 @@
       <c r="O68" t="n">
         <v>18</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.396649283144565</v>
       </c>
@@ -14229,9 +14127,6 @@
       <c r="O70" t="n">
         <v>16</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.3525771405729466</v>
       </c>
@@ -14625,9 +14520,6 @@
       <c r="O72" t="n">
         <v>13</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.2864689267155192</v>
       </c>
@@ -15021,9 +14913,6 @@
       <c r="O74" t="n">
         <v>12</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.2628887220519165</v>
       </c>
@@ -15417,9 +15306,6 @@
       <c r="O76" t="n">
         <v>11</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.2409813285475902</v>
       </c>
@@ -15813,9 +15699,6 @@
       <c r="O78" t="n">
         <v>24</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.5257774441038331</v>
       </c>
@@ -16209,9 +16092,6 @@
       <c r="O80" t="n">
         <v>14</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.3067035090605694</v>
       </c>
@@ -16605,9 +16485,6 @@
       <c r="O82" t="n">
         <v>13</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.284796115556243</v>
       </c>
@@ -17001,9 +16878,6 @@
       <c r="O84" t="n">
         <v>13</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0.284796115556243</v>
       </c>
@@ -17397,9 +17271,6 @@
       <c r="O86" t="n">
         <v>18</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.3943330830778749</v>
       </c>
@@ -17793,9 +17664,6 @@
       <c r="O88" t="n">
         <v>23</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.5038700505995067</v>
       </c>
@@ -18189,9 +18057,6 @@
       <c r="O90" t="n">
         <v>28</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.6134070181211387</v>
       </c>
@@ -18585,9 +18450,6 @@
       <c r="O92" t="n">
         <v>20</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.4381478700865276</v>
       </c>
@@ -18981,9 +18843,6 @@
       <c r="O94" t="n">
         <v>20</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.4381478700865276</v>
       </c>
@@ -19377,9 +19236,6 @@
       <c r="O96" t="n">
         <v>12</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.2628887220519165</v>
       </c>
@@ -19773,9 +19629,6 @@
       <c r="O98" t="n">
         <v>8</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.17422579772276</v>
       </c>
@@ -20169,9 +20022,6 @@
       <c r="O100" t="n">
         <v>13</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.2831169212994849</v>
       </c>
@@ -20565,9 +20415,6 @@
       <c r="O102" t="n">
         <v>17</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.3702298201608649</v>
       </c>
@@ -20961,9 +20808,6 @@
       <c r="O104" t="n">
         <v>22</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.4791209437375898</v>
       </c>
@@ -21357,9 +21201,6 @@
       <c r="O106" t="n">
         <v>10</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.2177822471534499</v>
       </c>
@@ -21753,9 +21594,6 @@
       <c r="O108" t="n">
         <v>10</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.2177822471534499</v>
       </c>
@@ -22149,9 +21987,6 @@
       <c r="O110" t="n">
         <v>19</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.4137862695915548</v>
       </c>
@@ -22545,9 +22380,6 @@
       <c r="O112" t="n">
         <v>39</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.8493507638984548</v>
       </c>
@@ -22941,9 +22773,6 @@
       <c r="O114" t="n">
         <v>28</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.6097902920296598</v>
       </c>
@@ -23337,9 +23166,6 @@
       <c r="O116" t="n">
         <v>24</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.5226773931682798</v>
       </c>
@@ -23733,9 +23559,6 @@
       <c r="O118" t="n">
         <v>24</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.5226773931682798</v>
       </c>
@@ -24128,9 +23951,6 @@
       </c>
       <c r="O120" t="n">
         <v>14</v>
-      </c>
-      <c r="Q120" t="n">
-        <v>0</v>
       </c>
       <c r="R120" t="n">
         <v>0.3048951460148299</v>
